--- a/public/templates/template_siswa.xlsx
+++ b/public/templates/template_siswa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\7-kaih\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED820AA-C158-4F56-B75E-FC4E7A57DCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5CC1BB-39B5-4D04-8801-7BC66CA50D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="21036" windowHeight="11748" xr2:uid="{77D49924-EE55-4257-BA6A-30F0A7773696}"/>
+    <workbookView xWindow="2004" yWindow="1212" windowWidth="21036" windowHeight="11748" xr2:uid="{77D49924-EE55-4257-BA6A-30F0A7773696}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Siswa Sekolah" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>NISN</t>
   </si>
@@ -63,9 +63,6 @@
     <t xml:space="preserve">Data Siswa </t>
   </si>
   <si>
-    <t>XXXXXXXXXX</t>
-  </si>
-  <si>
     <t>XI RPL 1</t>
   </si>
   <si>
@@ -73,6 +70,12 @@
   </si>
   <si>
     <t>Laki Laki/Perempuan</t>
+  </si>
+  <si>
+    <t>Tempat Lahir</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXX</t>
   </si>
 </sst>
 </file>
@@ -543,25 +546,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AE6492B-C77D-49CF-9B65-6A3CF8E268D3}">
-  <dimension ref="A1:CAO4"/>
+  <dimension ref="A1:CAP4"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="28.109375" customWidth="1"/>
     <col min="3" max="3" width="9.88671875" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" customWidth="1"/>
     <col min="5" max="5" width="14.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" customWidth="1"/>
-    <col min="7" max="7" width="24.77734375" customWidth="1"/>
-    <col min="8" max="2065" width="0" hidden="1" customWidth="1"/>
-    <col min="2066" max="2066" width="4.44140625" hidden="1" customWidth="1"/>
-    <col min="2067" max="2067" width="7.109375" hidden="1" customWidth="1"/>
-    <col min="2068" max="2068" width="12.21875" hidden="1" customWidth="1"/>
-    <col min="2069" max="2069" width="52.5546875" hidden="1" customWidth="1"/>
-    <col min="2070" max="2070" width="0" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="8" max="8" width="24.77734375" customWidth="1"/>
+    <col min="9" max="2066" width="0" hidden="1" customWidth="1"/>
+    <col min="2067" max="2067" width="4.44140625" hidden="1" customWidth="1"/>
+    <col min="2068" max="2068" width="7.109375" hidden="1" customWidth="1"/>
+    <col min="2069" max="2069" width="12.21875" hidden="1" customWidth="1"/>
+    <col min="2070" max="2070" width="52.5546875" hidden="1" customWidth="1"/>
+    <col min="2071" max="2071" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -571,8 +575,9 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
@@ -582,8 +587,9 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:7" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -600,33 +606,36 @@
         <v>4</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
       </c>
       <c r="D4">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
